--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_384_R41.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_384_R41.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6102</v>
+        <v>7.5554</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8896</v>
+        <v>3.7378</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7206</v>
+        <v>3.8176</v>
       </c>
       <c r="G2" t="n">
         <v>3.6018</v>
@@ -610,13 +610,13 @@
         <v>1.5923</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5544</v>
+        <v>1.4995</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5139</v>
+        <v>1.3621</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0405</v>
+        <v>0.1375</v>
       </c>
       <c r="V2" t="n">
         <v>0.8617</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3154</v>
+        <v>6.8272</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8327</v>
+        <v>4.1829</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4827</v>
+        <v>2.6443</v>
       </c>
       <c r="G3" t="n">
         <v>6.4163</v>
@@ -688,13 +688,13 @@
         <v>1.3648</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.3143</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8619</v>
+        <v>-0.5117</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0358</v>
+        <v>0.1974</v>
       </c>
       <c r="V3" t="n">
         <v>1.6352</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0824</v>
+        <v>4.7703</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7682</v>
+        <v>2.5853</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3142</v>
+        <v>2.1849</v>
       </c>
       <c r="G4" t="n">
         <v>4.9137</v>
@@ -766,13 +766,13 @@
         <v>1.1374</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0149</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0774</v>
+        <v>-0.2602</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4045</v>
+        <v>0.2752</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1583</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6336</v>
+        <v>3.1937</v>
       </c>
       <c r="E5" t="n">
-        <v>0.989</v>
+        <v>0.8723</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6446</v>
+        <v>2.3213</v>
       </c>
       <c r="G5" t="n">
         <v>1.9091</v>
@@ -844,13 +844,13 @@
         <v>1.5923</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1795</v>
+        <v>-0.2605</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1318</v>
+        <v>0.0151</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0477</v>
+        <v>-0.2755</v>
       </c>
       <c r="V5" t="n">
         <v>1.0901</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9958</v>
+        <v>1.3346</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4902</v>
+        <v>0.3035</v>
       </c>
       <c r="F6" t="n">
-        <v>1.486</v>
+        <v>1.0311</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7995</v>
+        <v>3.6339</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0187</v>
+        <v>0.3623</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7808</v>
+        <v>3.2716</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8745000000000001</v>
+        <v>2.6256</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6882</v>
+        <v>0.788</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1863</v>
+        <v>1.8376</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.075</v>
+        <v>1.0083</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6695</v>
+        <v>-0.4257</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5945</v>
+        <v>1.434</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2275</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R6" t="n">
         <v>0.9099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4238</v>
+        <v>0.1556</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2273</v>
+        <v>-0.5925</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6511</v>
+        <v>0.7481</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5451</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4173</v>
+        <v>0.5484</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6745</v>
+        <v>-1.0908</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0917</v>
+        <v>1.6392</v>
       </c>
       <c r="G7" t="n">
         <v>1.7796</v>
@@ -1000,13 +1000,13 @@
         <v>1.1374</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2728</v>
+        <v>0.404</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1492</v>
+        <v>-0.5655</v>
       </c>
       <c r="U7" t="n">
-        <v>1.422</v>
+        <v>0.9695</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6352</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3839</v>
+        <v>0.5214</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2153</v>
+        <v>-0.1306</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5992</v>
+        <v>0.652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8892</v>
+        <v>-0.8647</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9504</v>
+        <v>-0.2074</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0612</v>
+        <v>-0.6573</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8454</v>
+        <v>-0.6847</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8454</v>
+        <v>-0.0555</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6292</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0438</v>
+        <v>-0.18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.105</v>
+        <v>-0.1519</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0612</v>
+        <v>-0.028</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0407</v>
+        <v>-0.0689</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2873</v>
+        <v>0.0091</v>
       </c>
       <c r="U8" t="n">
-        <v>0.328</v>
+        <v>-0.0779</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7734</v>
+        <v>0.5451</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7734</v>
+        <v>0.5451</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2786</v>
+        <v>0.4194</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3969</v>
+        <v>-0.8404</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6756</v>
+        <v>1.2598</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6339</v>
+        <v>0.7995</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3623</v>
+        <v>0.0187</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2716</v>
+        <v>0.7808</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6256</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.788</v>
+        <v>0.6882</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8376</v>
+        <v>0.1863</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0083</v>
+        <v>-0.075</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4257</v>
+        <v>-0.6695</v>
       </c>
       <c r="O9" t="n">
-        <v>1.434</v>
+        <v>0.5945</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3648</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R9" t="n">
         <v>0.9099</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9003</v>
+        <v>-0.1527</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2929</v>
+        <v>-0.5775</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3925</v>
+        <v>0.4249</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5451</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2239</v>
+        <v>0.1576</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7143</v>
+        <v>-0.2153</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4904</v>
+        <v>0.373</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8647</v>
+        <v>0.8892</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2074</v>
+        <v>0.9504</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6573</v>
+        <v>-0.0612</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6847</v>
+        <v>0.8454</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0555</v>
+        <v>0.8454</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6292</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.18</v>
+        <v>0.0438</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1519</v>
+        <v>0.105</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.028</v>
+        <v>-0.0612</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8141</v>
+        <v>-0.1856</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5746</v>
+        <v>-0.2873</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2395</v>
+        <v>0.1017</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5451</v>
+        <v>-0.7734</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5451</v>
+        <v>-0.7734</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.7577</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4359</v>
+        <v>-3.4782</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5453</v>
+        <v>2.7204</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3073</v>
+        <v>1.189</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3139</v>
+        <v>0.8803</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0066</v>
+        <v>0.3087</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2867</v>
+        <v>-0.0531</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1208</v>
+        <v>1.756</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4075</v>
+        <v>-1.8091</v>
       </c>
       <c r="M11" t="n">
-        <v>1.594</v>
+        <v>1.242</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1931</v>
+        <v>-0.8758</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4008</v>
+        <v>2.1178</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2275</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R11" t="n">
         <v>1.3648</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3352</v>
+        <v>-0.2634</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0119</v>
+        <v>-0.377</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3234</v>
+        <v>0.1136</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0901</v>
+        <v>-0.7734</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8783</v>
+        <v>-0.8457</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1786</v>
+        <v>-2.5526</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3003</v>
+        <v>1.7069</v>
       </c>
       <c r="G12" t="n">
-        <v>1.189</v>
+        <v>0.3073</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8803</v>
+        <v>0.3139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3087</v>
+        <v>-0.0066</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0531</v>
+        <v>-1.2867</v>
       </c>
       <c r="K12" t="n">
-        <v>1.756</v>
+        <v>0.1208</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8091</v>
+        <v>-1.4075</v>
       </c>
       <c r="M12" t="n">
-        <v>1.242</v>
+        <v>1.594</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8758</v>
+        <v>0.1931</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1178</v>
+        <v>1.4008</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R12" t="n">
         <v>1.3648</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.384</v>
+        <v>-0.2903</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0774</v>
+        <v>-0.1286</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3066</v>
+        <v>-0.1618</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7734</v>
+        <v>-1.0901</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7734</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.72440000000001</v>
+        <v>23.7246</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3738</v>
+        <v>3.3739</v>
       </c>
       <c r="F13" t="n">
-        <v>20.3506</v>
+        <v>20.3505</v>
       </c>
       <c r="G13" t="n">
         <v>24.5747</v>
@@ -1459,7 +1459,7 @@
         <v>11.2271</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.5111</v>
@@ -1468,13 +1468,13 @@
         <v>12.511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5386000000000006</v>
+        <v>0.5383</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9142</v>
+        <v>-1.914</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4526</v>
+        <v>2.4527</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3884</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3069</v>
+        <v>4.072</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6082</v>
+        <v>3.3086</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6987</v>
+        <v>0.7633</v>
       </c>
       <c r="G14" t="n">
         <v>3.2098</v>
@@ -1546,13 +1546,13 @@
         <v>2.2747</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2379</v>
+        <v>-0.4729</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.4724</v>
+        <v>-0.772</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2344</v>
+        <v>0.2991</v>
       </c>
       <c r="V14" t="n">
         <v>4.7471</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3599</v>
+        <v>1.92</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.423</v>
+        <v>-0.5397</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7829</v>
+        <v>2.4597</v>
       </c>
       <c r="G15" t="n">
         <v>-2.6762</v>
@@ -1624,13 +1624,13 @@
         <v>2.0473</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1254</v>
+        <v>0.6854</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1913</v>
+        <v>-0.3081</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3167</v>
+        <v>0.9935</v>
       </c>
       <c r="V15" t="n">
         <v>1.8635</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.5957</v>
       </c>
       <c r="E16" t="n">
         <v>0.0216</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8327</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.0387</v>
@@ -1702,13 +1702,13 @@
         <v>0.6824</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2706</v>
+        <v>0.012</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2153</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4859</v>
+        <v>0.2273</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.832</v>
+        <v>-1.9955</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4301</v>
+        <v>-2.0138</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4018</v>
+        <v>0.0183</v>
       </c>
       <c r="G17" t="n">
         <v>-3.8249</v>
@@ -1780,13 +1780,13 @@
         <v>1.5923</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4479</v>
+        <v>0.2844</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5869</v>
+        <v>0.0032</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.139</v>
+        <v>0.2812</v>
       </c>
       <c r="V17" t="n">
         <v>1.0901</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8992</v>
+        <v>-2.6067</v>
       </c>
       <c r="E18" t="n">
-        <v>0.507</v>
+        <v>-2.766</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4062</v>
+        <v>0.1593</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6571</v>
+        <v>-2.346</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5719</v>
+        <v>-0.7467</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0852</v>
+        <v>-1.5993</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.415</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4523</v>
+        <v>-0.0266</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.7037</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.242</v>
+        <v>-1.6157</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1196</v>
+        <v>-0.7201</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1225</v>
+        <v>-0.8956</v>
       </c>
       <c r="P18" t="n">
         <v>0.6824</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6824</v>
+        <v>1.8198</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0273</v>
+        <v>-0.398</v>
       </c>
       <c r="T18" t="n">
-        <v>0.922</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1052</v>
+        <v>0.1136</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9519</v>
+        <v>-0.5451</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3867</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.9519</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5376</v>
+        <v>-2.9737</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7714</v>
+        <v>-1.3044</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7662</v>
+        <v>-1.6692</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1057</v>
@@ -1936,13 +1936,13 @@
         <v>0.2275</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.522</v>
+        <v>0.0419</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2753</v>
+        <v>0.1916</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2467</v>
+        <v>-0.1497</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7147</v>
+        <v>-3.124</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5831</v>
+        <v>-0.4269</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1316</v>
+        <v>-2.6971</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.346</v>
+        <v>-1.6571</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7467</v>
+        <v>-1.5719</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5993</v>
+        <v>-0.0852</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.415</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0266</v>
+        <v>-0.4523</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7037</v>
+        <v>0.0373</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6157</v>
+        <v>-1.242</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7201</v>
+        <v>-1.1196</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8956</v>
+        <v>-0.1225</v>
       </c>
       <c r="P20" t="n">
         <v>0.6824</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8198</v>
+        <v>0.6824</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5061</v>
+        <v>-0.1975</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3287</v>
+        <v>-0.0119</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1773</v>
+        <v>-0.1857</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5451</v>
+        <v>-1.9519</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3867</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1583</v>
+        <v>-1.9519</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.834</v>
+        <v>-5.6241</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6983</v>
+        <v>-4.1653</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1356</v>
+        <v>-1.4589</v>
       </c>
       <c r="G21" t="n">
         <v>-4.3419</v>
@@ -2092,13 +2092,13 @@
         <v>1.1374</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6881</v>
+        <v>0.898</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0897</v>
+        <v>0.6227</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5985</v>
+        <v>0.2752</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1802</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1531</v>
+        <v>-6.6142</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.5763</v>
+        <v>-3.4483</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4232</v>
+        <v>-3.166</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.3471</v>
+        <v>-5.5242</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0337</v>
+        <v>-2.5215</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.3134</v>
+        <v>-3.0027</v>
       </c>
       <c r="J22" t="n">
-        <v>-5.649</v>
+        <v>-3.1371</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7974</v>
+        <v>-1.4357</v>
       </c>
       <c r="L22" t="n">
-        <v>-4.8516</v>
+        <v>-1.7014</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-2.3871</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2363</v>
+        <v>-1.0858</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4618</v>
+        <v>-1.3013</v>
       </c>
       <c r="P22" t="n">
         <v>0.4549</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5923</v>
+        <v>0.4549</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7159</v>
+        <v>-0.4549</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7899</v>
+        <v>-0.3112</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0741</v>
+        <v>-0.1437</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5451</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2751</v>
+        <v>-7.374</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9152</v>
+        <v>-7.9265</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3599</v>
+        <v>0.5525</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.5242</v>
+        <v>-6.3471</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5215</v>
+        <v>-1.0337</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0027</v>
+        <v>-5.3134</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1371</v>
+        <v>-5.649</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.4357</v>
+        <v>-0.7974</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.7014</v>
+        <v>-4.8516</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3871</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0858</v>
+        <v>-0.2363</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3013</v>
+        <v>-0.4618</v>
       </c>
       <c r="P23" t="n">
         <v>0.4549</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4549</v>
+        <v>1.5923</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1157</v>
+        <v>-0.9368</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7781</v>
+        <v>-1.1402</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3377</v>
+        <v>0.2033</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0901</v>
+        <v>-0.5451</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.7246</v>
+        <v>-23.7245</v>
       </c>
       <c r="E24" t="n">
-        <v>-19.2606</v>
+        <v>-19.2607</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.463799999999999</v>
+        <v>-4.463999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-24.5746</v>
@@ -2326,10 +2326,10 @@
         <v>12.511</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5383</v>
+        <v>-0.5384</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4524</v>
+        <v>-2.4528</v>
       </c>
       <c r="U24" t="n">
         <v>1.9141</v>
